--- a/Test Results/Excel/Selenium_Summary.xlsx
+++ b/Test Results/Excel/Selenium_Summary.xlsx
@@ -46,7 +46,7 @@
     <t>Pass Percentage (%)</t>
   </si>
   <si>
-    <t>0%</t>
+    <t>10%</t>
   </si>
 </sst>
 </file>
@@ -469,7 +469,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -477,7 +477,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -485,7 +485,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">

--- a/Test Results/Excel/Selenium_Summary.xlsx
+++ b/Test Results/Excel/Selenium_Summary.xlsx
@@ -46,7 +46,7 @@
     <t>Pass Percentage (%)</t>
   </si>
   <si>
-    <t>10%</t>
+    <t>100%</t>
   </si>
 </sst>
 </file>
@@ -469,7 +469,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -477,7 +477,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -485,7 +485,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">

--- a/Test Results/Excel/Selenium_Summary.xlsx
+++ b/Test Results/Excel/Selenium_Summary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Metric</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>Not Applicable</t>
+  </si>
+  <si>
+    <t>Not Run</t>
   </si>
   <si>
     <t>Pass Percentage (%)</t>
@@ -433,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -461,7 +464,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -469,7 +472,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -477,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -493,7 +496,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -501,7 +504,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -509,15 +512,23 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
